--- a/artfynd/A 58378-2025 artfynd.xlsx
+++ b/artfynd/A 58378-2025 artfynd.xlsx
@@ -675,45 +675,42 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129950613</v>
+        <v>129950570</v>
       </c>
       <c r="B2" t="n">
-        <v>91836</v>
+        <v>56927</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1101</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -721,13 +718,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>580906</v>
+        <v>580790</v>
       </c>
       <c r="R2" t="n">
-        <v>6431252</v>
+        <v>6431393</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -761,7 +758,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>I/vid roten av granlåga</t>
+          <t>Suttit på tallåga</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,7 +767,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -789,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129950570</v>
+        <v>129950596</v>
       </c>
       <c r="B3" t="n">
-        <v>56926</v>
+        <v>56927</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -822,7 +818,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -832,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>580790</v>
+        <v>580836</v>
       </c>
       <c r="R3" t="n">
-        <v>6431393</v>
+        <v>6431368</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -868,11 +864,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-12-02</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Suttit på tallåga</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,42 +890,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129950596</v>
+        <v>129950576</v>
       </c>
       <c r="B4" t="n">
-        <v>56926</v>
+        <v>79703</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -942,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>580836</v>
+        <v>580790</v>
       </c>
       <c r="R4" t="n">
-        <v>6431368</v>
+        <v>6431393</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -980,12 +966,18 @@
           <t>2025-12-02</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På tallåga</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1004,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129950576</v>
+        <v>129950582</v>
       </c>
       <c r="B5" t="n">
-        <v>79700</v>
+        <v>92922</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1015,25 +1007,33 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
@@ -1078,11 +1078,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-12-02</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På tallåga</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1110,10 +1105,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129950582</v>
+        <v>129950522</v>
       </c>
       <c r="B6" t="n">
-        <v>92919</v>
+        <v>57734</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1121,34 +1116,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5966</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1156,13 +1148,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>580790</v>
+        <v>580919</v>
       </c>
       <c r="R6" t="n">
-        <v>6431393</v>
+        <v>6431275</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1194,13 +1186,17 @@
           <t>2025-12-02</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Bearbetat tallåga</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1219,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129950522</v>
+        <v>129950613</v>
       </c>
       <c r="B7" t="n">
-        <v>57733</v>
+        <v>91839</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1230,31 +1226,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>1101</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Peck) Jülich</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1262,10 +1261,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>580919</v>
+        <v>580906</v>
       </c>
       <c r="R7" t="n">
-        <v>6431275</v>
+        <v>6431252</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1302,7 +1301,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Bearbetat tallåga</t>
+          <t>I/vid roten av granlåga</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1311,6 +1310,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 58378-2025 artfynd.xlsx
+++ b/artfynd/A 58378-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129950570</v>
       </c>
       <c r="B2" t="n">
-        <v>56927</v>
+        <v>56930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>129950596</v>
       </c>
       <c r="B3" t="n">
-        <v>56927</v>
+        <v>56930</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>129950576</v>
       </c>
       <c r="B4" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>129950582</v>
       </c>
       <c r="B5" t="n">
-        <v>92922</v>
+        <v>92925</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>129950522</v>
       </c>
       <c r="B6" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>129950613</v>
       </c>
       <c r="B7" t="n">
-        <v>91839</v>
+        <v>91842</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 58378-2025 artfynd.xlsx
+++ b/artfynd/A 58378-2025 artfynd.xlsx
@@ -893,7 +893,7 @@
         <v>129950576</v>
       </c>
       <c r="B4" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>129950582</v>
       </c>
       <c r="B5" t="n">
-        <v>92925</v>
+        <v>92926</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>129950613</v>
       </c>
       <c r="B7" t="n">
-        <v>91842</v>
+        <v>91843</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 58378-2025 artfynd.xlsx
+++ b/artfynd/A 58378-2025 artfynd.xlsx
@@ -893,7 +893,7 @@
         <v>129950576</v>
       </c>
       <c r="B4" t="n">
-        <v>79707</v>
+        <v>79708</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>129950582</v>
       </c>
       <c r="B5" t="n">
-        <v>92926</v>
+        <v>92943</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>129950613</v>
       </c>
       <c r="B7" t="n">
-        <v>91843</v>
+        <v>91860</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 58378-2025 artfynd.xlsx
+++ b/artfynd/A 58378-2025 artfynd.xlsx
@@ -999,7 +999,7 @@
         <v>129950582</v>
       </c>
       <c r="B5" t="n">
-        <v>92959</v>
+        <v>92961</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>129950613</v>
       </c>
       <c r="B7" t="n">
-        <v>91876</v>
+        <v>91878</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 58378-2025 artfynd.xlsx
+++ b/artfynd/A 58378-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129950570</v>
       </c>
       <c r="B2" t="n">
-        <v>56931</v>
+        <v>57016</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>129950596</v>
       </c>
       <c r="B3" t="n">
-        <v>56931</v>
+        <v>57016</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>129950576</v>
       </c>
       <c r="B4" t="n">
-        <v>79714</v>
+        <v>79799</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>129950582</v>
       </c>
       <c r="B5" t="n">
-        <v>92961</v>
+        <v>93048</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>129950522</v>
       </c>
       <c r="B6" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>129950613</v>
       </c>
       <c r="B7" t="n">
-        <v>91878</v>
+        <v>91965</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 58378-2025 artfynd.xlsx
+++ b/artfynd/A 58378-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129950570</v>
       </c>
       <c r="B2" t="n">
-        <v>57016</v>
+        <v>56931</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>129950596</v>
       </c>
       <c r="B3" t="n">
-        <v>57016</v>
+        <v>56931</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>129950576</v>
       </c>
       <c r="B4" t="n">
-        <v>79799</v>
+        <v>79714</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>129950582</v>
       </c>
       <c r="B5" t="n">
-        <v>93048</v>
+        <v>92961</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>129950522</v>
       </c>
       <c r="B6" t="n">
-        <v>57823</v>
+        <v>57738</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 58378-2025 artfynd.xlsx
+++ b/artfynd/A 58378-2025 artfynd.xlsx
@@ -675,42 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129950570</v>
+        <v>129950613</v>
       </c>
       <c r="B2" t="n">
-        <v>57016</v>
+        <v>92147</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>1101</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Peck) Jülich</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,13 +721,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>580790</v>
+        <v>580906</v>
       </c>
       <c r="R2" t="n">
-        <v>6431393</v>
+        <v>6431252</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -758,7 +761,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Suttit på tallåga</t>
+          <t>I/vid roten av granlåga</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -767,6 +770,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -785,42 +789,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129950596</v>
+        <v>129950582</v>
       </c>
       <c r="B3" t="n">
-        <v>57016</v>
+        <v>93235</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>5966</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -828,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>580836</v>
+        <v>580790</v>
       </c>
       <c r="R3" t="n">
-        <v>6431368</v>
+        <v>6431393</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -872,6 +879,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -893,7 +901,7 @@
         <v>129950576</v>
       </c>
       <c r="B4" t="n">
-        <v>79799</v>
+        <v>79946</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,45 +1004,42 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129950582</v>
+        <v>129950522</v>
       </c>
       <c r="B5" t="n">
-        <v>93048</v>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1042,13 +1047,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>580790</v>
+        <v>580919</v>
       </c>
       <c r="R5" t="n">
-        <v>6431393</v>
+        <v>6431275</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1080,13 +1085,17 @@
           <t>2025-12-02</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Bearbetat tallåga</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1105,32 +1114,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129950522</v>
+        <v>129950570</v>
       </c>
       <c r="B6" t="n">
-        <v>57823</v>
+        <v>57141</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,7 +1147,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1148,13 +1157,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>580919</v>
+        <v>580790</v>
       </c>
       <c r="R6" t="n">
-        <v>6431275</v>
+        <v>6431393</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1188,7 +1197,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Bearbetat tallåga</t>
+          <t>Suttit på tallåga</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1215,45 +1224,42 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129950613</v>
+        <v>129950596</v>
       </c>
       <c r="B7" t="n">
-        <v>91965</v>
+        <v>57141</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1101</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1261,13 +1267,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>580906</v>
+        <v>580836</v>
       </c>
       <c r="R7" t="n">
-        <v>6431252</v>
+        <v>6431368</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1299,18 +1305,12 @@
           <t>2025-12-02</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>I/vid roten av granlåga</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
